--- a/artfynd/A 7616-2024 artfynd.xlsx
+++ b/artfynd/A 7616-2024 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>121187728</v>
       </c>
       <c r="B4" t="n">
-        <v>99232</v>
+        <v>99242</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7616-2024 artfynd.xlsx
+++ b/artfynd/A 7616-2024 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>121187728</v>
       </c>
       <c r="B4" t="n">
-        <v>99242</v>
+        <v>99255</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7616-2024 artfynd.xlsx
+++ b/artfynd/A 7616-2024 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>121187728</v>
       </c>
       <c r="B4" t="n">
-        <v>99255</v>
+        <v>99256</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7616-2024 artfynd.xlsx
+++ b/artfynd/A 7616-2024 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>121187728</v>
       </c>
       <c r="B4" t="n">
-        <v>99256</v>
+        <v>99259</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7616-2024 artfynd.xlsx
+++ b/artfynd/A 7616-2024 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>121187728</v>
       </c>
       <c r="B4" t="n">
-        <v>99259</v>
+        <v>99265</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7616-2024 artfynd.xlsx
+++ b/artfynd/A 7616-2024 artfynd.xlsx
@@ -675,56 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102176545</v>
+        <v>102176559</v>
       </c>
       <c r="B2" t="n">
-        <v>41765</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100768</v>
+        <v>1855</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flenörtskapuschongfly</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cucullia scrophulariae</t>
+          <t>Anthemis arvensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -732,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406352.5513082308</v>
+        <v>406353</v>
       </c>
       <c r="R2" t="n">
-        <v>6204286.529523259</v>
+        <v>6204287</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,19 +755,9 @@
           <t>2022-07-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -825,37 +805,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102176559</v>
+        <v>116599696</v>
       </c>
       <c r="B3" t="n">
-        <v>104790</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1855</v>
+        <v>208255</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anthemis arvensis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -863,27 +838,36 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>600 m O Bjäret, Sk</t>
+          <t>FrostaV_3, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406352.5513082308</v>
+        <v>406314</v>
       </c>
       <c r="R3" t="n">
-        <v>6204286.529523259</v>
+        <v>6204452</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -907,22 +891,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-10</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,35 +919,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>längs skogsbilväg</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>flenört</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Scrophularia nodosa</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Scrophularia nodosa</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Torbjörn Tyler</t>
+          <t>Erik Böös</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Torbjörn Tyler</t>
+          <t>Erik Böös</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -973,12 +937,7 @@
         <v>121187728</v>
       </c>
       <c r="B4" t="n">
-        <v>99265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 7616-2024 artfynd.xlsx
+++ b/artfynd/A 7616-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102176559</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -931,6 +941,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116599696</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,8 +1052,18 @@
           <t>Skånes Flora, Höör socken, 1946-1947</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121187728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>